--- a/out/LSTM-Mamba1_repeat_5_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001309930757600814</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1504858845091177</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1507437838550194</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4563257889714621</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8815939771807737</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7627844707916938</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03251311665591503</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3707524774976536</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05701705702885747</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4522625513204825</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06926899062906326</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5337780503465315</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01833031046867782</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5010812424944351</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01018341816259477</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5031003217257061</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02139549778580887</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5357225572604134</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008403484173615553</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5311136577189609</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005982249854186671</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5346728957648005</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002352299121195953</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5333888581231306</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001332946628964219</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5337010786432203</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005046762461158673</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5333764149258756</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002339084162213094</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5333391929694272</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5332702743028414</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5332291838216928</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5332241637163579</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5332201816317658</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.533217746961575</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5332122297195853</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5332059057255774</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.533200537936999</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5332005746854906</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5332006849309663</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5332007584279499</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5332024856070655</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5332052049954605</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5332065646896579</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5332043597801486</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5332036615588038</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5332033308223775</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.533203036834443</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5332025591040491</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5332025223555574</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.533202191619131</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5332031470799183</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5332027795950002</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5332032205769022</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.533202595852541</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5332024121100819</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5332020078766718</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5332011259128682</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5332013096553273</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5332016403917538</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5332015301462782</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5332014933977863</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5332014199008026</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5332013831523109</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5332010891643763</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5332010156673926</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.533201346403819</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001309930757600814</v>
+        <v>-0.0001250325101115741</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1504858845091177</v>
+        <v>-0.1436383394110767</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.2010084100773801</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.2010084100773801</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1507437838550194</v>
+        <v>-0.1438629961504316</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4563257889714621</v>
+        <v>0.3582260398764504</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8815939771807737</v>
+        <v>-0.00100841007738009</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7627844707916938</v>
+        <v>0.5732768907168205</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03251311665591503</v>
+        <v>0.02552353012951869</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3707524774976536</v>
+        <v>0.2655232772120235</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05701705702885747</v>
+        <v>0.04475944712188486</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4522625513204825</v>
+        <v>0.3295103804709939</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06926899062906326</v>
+        <v>0.05437744220433369</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5337780503465315</v>
+        <v>0.3935019263575594</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01833031046867782</v>
+        <v>0.01438979865786775</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5010812424944351</v>
+        <v>0.3678340315038071</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01018341816259477</v>
+        <v>0.007993188915153522</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5031003217257061</v>
+        <v>0.3694179894571016</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02139549778580887</v>
+        <v>0.01679588951136599</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5357225572604134</v>
+        <v>0.395027343259352</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008403484173615553</v>
+        <v>0.006595351252514011</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5311136577189609</v>
+        <v>0.3914081204732475</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005982249854186671</v>
+        <v>0.004695448243347358</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5346728957648005</v>
+        <v>0.3942014300313464</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002352299121195953</v>
+        <v>0.001845805704026546</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5333888581231306</v>
+        <v>0.3931922086571553</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001332946628964219</v>
+        <v>0.001044702366733449</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5337010786432203</v>
+        <v>0.3934362716325417</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005046762461158673</v>
+        <v>0.0003954599076624671</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5333764149258756</v>
+        <v>0.3931801072831992</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002339084162213094</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5333391929694272</v>
+        <v>0.3931497907788598</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5332702743028414</v>
+        <v>0.3930944218123572</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5332291838216928</v>
+        <v>0.3930609464600782</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5332241637163579</v>
+        <v>0.3930559308225955</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5332201816317658</v>
+        <v>0.3930517306132731</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.533217746961575</v>
+        <v>0.3930487467341675</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5332122297195853</v>
+        <v>0.3930433029891611</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5332059057255774</v>
+        <v>0.3930373102557307</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.533200537936999</v>
+        <v>0.3930319424671524</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5332005746854906</v>
+        <v>0.3930319792156441</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5332006849309663</v>
+        <v>0.3930320894611196</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5332007584279499</v>
+        <v>0.3930321629581032</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3930323467005624</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5332024856070655</v>
+        <v>0.3930338901372188</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3930353600768919</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5332052049954605</v>
+        <v>0.393036609525614</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5332065646896579</v>
+        <v>0.3930379692198113</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5332043597801486</v>
+        <v>0.393035764310302</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3930353600768919</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.39303451486158</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5332036615588038</v>
+        <v>0.3930350660889572</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5332033308223775</v>
+        <v>0.3930347353525309</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.533203036834443</v>
+        <v>0.3930344413645964</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.39303451486158</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.393034073879678</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5332025591040491</v>
+        <v>0.3930339636342025</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5332025223555574</v>
+        <v>0.3930339268857108</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.393034073879678</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.533202191619131</v>
+        <v>0.3930335961492844</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5332031470799183</v>
+        <v>0.3930345516100717</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.39303451486158</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5332027795950002</v>
+        <v>0.3930341841251536</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5332032205769022</v>
+        <v>0.3930346251070556</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.533202595852541</v>
+        <v>0.3930340003826944</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5332024121100819</v>
+        <v>0.3930338166402352</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5332020078766718</v>
+        <v>0.3930334124068252</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3930325671915132</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5332011259128682</v>
+        <v>0.3930325304430216</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.3930326774369888</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3930326039400052</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.3930326774369888</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5332013096553273</v>
+        <v>0.3930327141854807</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3930326039400052</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5332016403917538</v>
+        <v>0.3930330449219071</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5332015301462782</v>
+        <v>0.3930329346764316</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5332014933977863</v>
+        <v>0.3930328979279397</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5332014199008026</v>
+        <v>0.3930328244309561</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5332013831523109</v>
+        <v>0.3930327876824644</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3930325671915132</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5332010891643763</v>
+        <v>0.3930324936945296</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5332010156673926</v>
+        <v>0.393032420197546</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3930324569460379</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3930323467005624</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3930324569460379</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.533201346403819</v>
+        <v>0.3930327509339724</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01736868172883987</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01008506119251251</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.006522839888930321</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.00446617603302002</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002734554931521416</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.001584015786647797</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.001073524355888367</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0008229874074459076</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0008778087794780731</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0009836405515670776</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.097446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001268699765205383</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.097446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001448914408683777</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001599950715899467</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.097446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001669736579060555</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.097446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001849686726927757</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001720918342471123</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.00156950019299984</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001543214544653893</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001644086092710495</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001807397231459618</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001926625147461891</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002105005085468292</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002231614664196968</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002434594556689262</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.00246984139084816</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002490172162652016</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.097446509901492</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002487683668732643</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.097446509901492</v>
+        <v>0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002556212246417999</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.097446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002659911289811134</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.097446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002794237807393074</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.097446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.003240298479795456</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002973182126879692</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00270598940551281</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002517728134989738</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.097446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002301847562193871</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.097446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002330821007490158</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.00223846547305584</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002171831205487251</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.00233842246234417</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002411607652902603</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002349652349948883</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002325490117073059</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002462234348058701</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002115359529852867</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001250325101115741</v>
+        <v>-8.677021837199572e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1436383394110767</v>
+        <v>-0.0996823151528278</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0008644871413707733</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0002627428621053696</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0004134178161621094</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2010084100773801</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0006349962204694748</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0007034707814455032</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0005649756640195847</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0003955680876970291</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-4.923716187477112e-05</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2010084100773801</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>9.56561416387558e-05</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0001777727156877518</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.000143442302942276</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>6.379745900630951e-05</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>5.356781184673309e-05</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.09976908537119976</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0002627037465572357</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1438629961504316</v>
+        <v>-0.09983640019362326</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3582260398764504</v>
+        <v>0.2420487711163884</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0002394448965787888</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.00100841007738009</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5732768907168205</v>
+        <v>0.3847258845432196</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02552353012951869</v>
+        <v>0.01724588753620422</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0005590002983808517</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2655232772120235</v>
+        <v>0.1767806890374937</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04475944712188486</v>
+        <v>0.03024341070049998</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0006259921938180923</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3295103804709939</v>
+        <v>0.220016051291608</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05437744220433369</v>
+        <v>0.03674217228264796</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001127896830439568</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3935019263575594</v>
+        <v>0.2632544749647521</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01438979865786775</v>
+        <v>0.009722084666365155</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001675279811024666</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3678340315038071</v>
+        <v>0.2459100827032754</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007993188915153522</v>
+        <v>0.005399399839875535</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001234641298651695</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3694179894571016</v>
+        <v>0.2469787462787987</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01679588951136599</v>
+        <v>0.01134750797502474</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001320065930485725</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.395027343259352</v>
+        <v>0.2642817883356363</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006595351252514011</v>
+        <v>0.004455384158350294</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.001783145591616631</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3914081204732475</v>
+        <v>0.261834593029404</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004695448243347358</v>
+        <v>0.003170605583854123</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002747522667050362</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3942014300313464</v>
+        <v>0.2637202875966686</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001845805704026546</v>
+        <v>0.001245617794136793</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003311401233077049</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3931922086571553</v>
+        <v>0.2630367198155753</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001044702366733449</v>
+        <v>0.0007040500568243558</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.003927541896700859</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3934362716325417</v>
+        <v>0.2632000158152247</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003954599076624671</v>
+        <v>0.000265104923056796</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004293167963624001</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3931801072831992</v>
+        <v>0.2630252412911607</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001821632753807493</v>
+        <v>0.0001216104509928598</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.004470249637961388</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3931497907788598</v>
+        <v>0.263003091642142</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.362265002008783e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004356252029538155</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3930944218123572</v>
+        <v>0.2629639228332366</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.003957508131861687</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3930609464600782</v>
+        <v>0.2629397185258858</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003502825275063515</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3930559308225955</v>
+        <v>0.2629347081008973</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003004821017384529</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3930517306132731</v>
+        <v>0.262930253807093</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002854982390999794</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3930487467341675</v>
+        <v>0.2629267197098411</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002800473943352699</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3930433029891611</v>
+        <v>0.2629214238798369</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002667354419827461</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3930373102557307</v>
+        <v>0.2629157618828332</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002403641119599342</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3930319424671524</v>
+        <v>0.262915578140374</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002103986218571663</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3930319792156441</v>
+        <v>0.2629156148888657</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001864945515990257</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3930320894611196</v>
+        <v>0.2629157251343413</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001770215108990669</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3930321629581032</v>
+        <v>0.2629157986313249</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0013583954423666</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3930323467005624</v>
+        <v>0.2629159823737841</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001036224886775017</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3930338901372188</v>
+        <v>0.2629175258104405</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.00178041122853756</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3930353600768919</v>
+        <v>0.2629189957501136</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002761581912636757</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.393036609525614</v>
+        <v>0.2629202451988356</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003287700936198235</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3930379692198113</v>
+        <v>0.2629216048930329</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.005276264622807503</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.393035764310302</v>
+        <v>0.2629193999835236</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006694307550787926</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3930353600768919</v>
+        <v>0.2629189957501136</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007478931918740273</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.39303451486158</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008144306018948555</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3930350660889572</v>
+        <v>0.2629187017621789</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.008491704240441322</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3930347353525309</v>
+        <v>0.2629183710257525</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.008286034688353539</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3930344413645964</v>
+        <v>0.2629180770378181</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.008152289316058159</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.39303451486158</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00782204233109951</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.393034073879678</v>
+        <v>0.2629177095528997</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.007415676489472389</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3930339636342025</v>
+        <v>0.2629175993074241</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.006872205063700676</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3930339268857108</v>
+        <v>0.2629175625589324</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.006600575521588326</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.393034073879678</v>
+        <v>0.2629177095528997</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005513666197657585</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3930335961492844</v>
+        <v>0.262917231822506</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.004920205101370811</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3930345516100717</v>
+        <v>0.2629181872832934</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005566978827118874</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.39303451486158</v>
+        <v>0.2629181505348017</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00612153671681881</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3930341841251536</v>
+        <v>0.2629178197983753</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006552131846547127</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3930346251070556</v>
+        <v>0.2629182607802772</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.006778253242373466</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3930340003826944</v>
+        <v>0.2629176360559161</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.006692292168736458</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3930338166402352</v>
+        <v>0.2629174523134569</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006507372483611107</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3930334124068252</v>
+        <v>0.2629170480800469</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006017310544848442</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3930325671915132</v>
+        <v>0.2629162028647349</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005275247618556023</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3930325304430216</v>
+        <v>0.2629161661162432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004621980711817741</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3930326774369888</v>
+        <v>0.2629163131102105</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004115017130970955</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3930326039400052</v>
+        <v>0.2629162396132269</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003355586901307106</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3930326774369888</v>
+        <v>0.2629163131102105</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003349201753735542</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3930327141854807</v>
+        <v>0.2629163498587024</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003060190007090569</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3930326039400052</v>
+        <v>0.2629162396132269</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003265568986535072</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3930330449219071</v>
+        <v>0.2629166805951288</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003381500020623207</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3930329346764316</v>
+        <v>0.2629165703496533</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003560969606041908</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3930328979279397</v>
+        <v>0.2629165336011614</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003604026511311531</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3930328244309561</v>
+        <v>0.2629164601041777</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003611652180552483</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3930327876824644</v>
+        <v>0.262916423355686</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003569101914763451</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3930325671915132</v>
+        <v>0.2629162028647349</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003309013321995735</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3930324936945296</v>
+        <v>0.2629161293677513</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003087164834141731</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.393032420197546</v>
+        <v>0.2629160558707677</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.00294681079685688</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3930324569460379</v>
+        <v>0.2629160926192596</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00267673097550869</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3930323467005624</v>
+        <v>0.2629159823737841</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00226103700697422</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3930324569460379</v>
+        <v>0.2629160926192596</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002160606905817986</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3930327509339724</v>
+        <v>0.2629163866071941</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_5_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_5_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01736868172883987</v>
+        <v>0.01736866310238838</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.01008506119251251</v>
+        <v>0.01008500345051289</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.006522839888930321</v>
+        <v>0.006522785872220993</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.00446617603302002</v>
+        <v>0.004466131329536438</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.002734554931521416</v>
+        <v>0.002734504640102386</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.3</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.001584015786647797</v>
+        <v>0.001583956182003021</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.001073524355888367</v>
+        <v>0.001073490828275681</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.0008229874074459076</v>
+        <v>0.0008230023086071014</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.0008778087794780731</v>
+        <v>0.0008777827024459839</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.0009836405515670776</v>
+        <v>0.0009835995733737946</v>
       </c>
       <c r="JB11" t="n">
         <v>0.4399999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.001268699765205383</v>
+        <v>0.001268738880753517</v>
       </c>
       <c r="JB12" t="n">
         <v>0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.001448914408683777</v>
+        <v>0.00144890695810318</v>
       </c>
       <c r="JB13" t="n">
         <v>0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001599950715899467</v>
+        <v>0.001599967479705811</v>
       </c>
       <c r="JB14" t="n">
         <v>0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.001669736579060555</v>
+        <v>0.001669749617576599</v>
       </c>
       <c r="JB15" t="n">
         <v>0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001849686726927757</v>
+        <v>0.001849718391895294</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.001720918342471123</v>
+        <v>0.001720894128084183</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.00156950019299984</v>
+        <v>0.00156952440738678</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001543214544653893</v>
+        <v>0.001543212682008743</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001644086092710495</v>
+        <v>0.001644076779484749</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.001807397231459618</v>
+        <v>0.001807363703846931</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001926625147461891</v>
+        <v>0.001926662400364876</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.002105005085468292</v>
+        <v>0.002104992046952248</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.002231614664196968</v>
+        <v>0.002231527119874954</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.002434594556689262</v>
+        <v>0.002434583380818367</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.00246984139084816</v>
+        <v>0.002469815313816071</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.002490172162652016</v>
+        <v>0.00249018520116806</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.002487683668732643</v>
+        <v>0.002487681806087494</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.16</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.002556212246417999</v>
+        <v>0.002556247636675835</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.3</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.002659911289811134</v>
+        <v>0.002659860998392105</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.002794237807393074</v>
+        <v>0.002794206142425537</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.003240298479795456</v>
+        <v>0.003240307793021202</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.002973182126879692</v>
+        <v>0.002973178401589394</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.00270598940551281</v>
+        <v>0.00270596519112587</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.002517728134989738</v>
+        <v>0.002517657354474068</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.002301847562193871</v>
+        <v>0.002301806584000587</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.002330821007490158</v>
+        <v>0.002330813556909561</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.00223846547305584</v>
+        <v>0.002238444983959198</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.002171831205487251</v>
+        <v>0.002171836793422699</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.00233842246234417</v>
+        <v>0.002338407561182976</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.002411607652902603</v>
+        <v>0.002411581575870514</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.16</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.002349652349948883</v>
+        <v>0.002349698916077614</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.16</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.002325490117073059</v>
+        <v>0.002325518056750298</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002462234348058701</v>
+        <v>0.002462219446897507</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.002115359529852867</v>
+        <v>0.002115311101078987</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0008644871413707733</v>
+        <v>0.000864468514919281</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.0002627428621053696</v>
+        <v>0.0002627056092023849</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0004134178161621094</v>
+        <v>-0.0004134681075811386</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0006349962204694748</v>
+        <v>-0.0006350204348564148</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.0007034707814455032</v>
+        <v>-0.0007034912705421448</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0005649756640195847</v>
+        <v>-0.00056501105427742</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0003955680876970291</v>
+        <v>-0.0003955811262130737</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-4.923716187477112e-05</v>
+        <v>-4.925765097141266e-05</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>9.56561416387558e-05</v>
+        <v>9.565427899360657e-05</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.0001777727156877518</v>
+        <v>0.0001777857542037964</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.000143442302942276</v>
+        <v>0.0001434348523616791</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>6.379745900630951e-05</v>
+        <v>6.377696990966797e-05</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>5.356781184673309e-05</v>
+        <v>5.355849862098694e-05</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0002627037465572357</v>
+        <v>0.0002626683562994003</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0002394448965787888</v>
+        <v>-0.0002395398914813995</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0005590002983808517</v>
+        <v>-0.0005590766668319702</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.0006259921938180923</v>
+        <v>-0.0006260499358177185</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001127896830439568</v>
+        <v>-0.001127965748310089</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001675279811024666</v>
+        <v>-0.00167534127831459</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001234641298651695</v>
+        <v>-0.001234740018844604</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.001320065930485725</v>
+        <v>-0.001320216804742813</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.001783145591616631</v>
+        <v>-0.001783240586519241</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002747522667050362</v>
+        <v>-0.002747606486082077</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003311401233077049</v>
+        <v>-0.003311436623334885</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.003927541896700859</v>
+        <v>-0.003927551209926605</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.004293167963624001</v>
+        <v>-0.004293181002140045</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.004470249637961388</v>
+        <v>-0.004470270127058029</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.004356252029538155</v>
+        <v>-0.004356198012828827</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.003957508131861687</v>
+        <v>-0.003957472741603851</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.003502825275063515</v>
+        <v>-0.003502827137708664</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003004821017384529</v>
+        <v>-0.003004826605319977</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.002854982390999794</v>
+        <v>-0.002855021506547928</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002800473943352699</v>
+        <v>-0.002800505608320236</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002667354419827461</v>
+        <v>-0.002667378634214401</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002403641119599342</v>
+        <v>-0.002403661608695984</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.2599999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002103986218571663</v>
+        <v>-0.002103995531797409</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.1199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.001864945515990257</v>
+        <v>-0.001864977180957794</v>
       </c>
       <c r="JB82" t="n">
         <v>0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.001770215108990669</v>
+        <v>-0.001770220696926117</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.0013583954423666</v>
+        <v>-0.001358415931463242</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001036224886775017</v>
+        <v>-0.001036189496517181</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.00178041122853756</v>
+        <v>-0.001780394464731216</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.002761581912636757</v>
+        <v>-0.00276164710521698</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.003287700936198235</v>
+        <v>-0.003287728875875473</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.005276264622807503</v>
+        <v>-0.005276300013065338</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.006694307550787926</v>
+        <v>-0.006694398820400238</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.007478931918740273</v>
+        <v>-0.007478851824998856</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.008144306018948555</v>
+        <v>-0.008144360035657883</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.008491704240441322</v>
+        <v>-0.008491922169923782</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.008286034688353539</v>
+        <v>-0.008286215364933014</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.008152289316058159</v>
+        <v>-0.008152246475219727</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00782204233109951</v>
+        <v>-0.007822047919034958</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.007415676489472389</v>
+        <v>-0.007415618747472763</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.006872205063700676</v>
+        <v>-0.006872124969959259</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.006600575521588326</v>
+        <v>-0.006600651890039444</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005513666197657585</v>
+        <v>-0.005513846874237061</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.004920205101370811</v>
+        <v>-0.004920367151498795</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005566978827118874</v>
+        <v>-0.005567163228988647</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.00612153671681881</v>
+        <v>-0.006121661514043808</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.006552131846547127</v>
+        <v>-0.006552185863256454</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.006778253242373466</v>
+        <v>-0.006778273731470108</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.006692292168736458</v>
+        <v>-0.006692253053188324</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.006507372483611107</v>
+        <v>-0.006507407873868942</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.2599999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.006017310544848442</v>
+        <v>-0.006017368286848068</v>
       </c>
       <c r="JB108" t="n">
         <v>0.02000000000000007</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.005275247618556023</v>
+        <v>-0.005275275558233261</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.004621980711817741</v>
+        <v>-0.004622001200914383</v>
       </c>
       <c r="JB110" t="n">
         <v>0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.004115017130970955</v>
+        <v>-0.004115030169487</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003355586901307106</v>
+        <v>-0.003355547785758972</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003349201753735542</v>
+        <v>-0.003349192440509796</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003060190007090569</v>
+        <v>-0.003060191869735718</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003265568986535072</v>
+        <v>-0.003265503793954849</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003381500020623207</v>
+        <v>-0.003381401300430298</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003560969606041908</v>
+        <v>-0.003560975193977356</v>
       </c>
       <c r="JB117" t="n">
         <v>0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003604026511311531</v>
+        <v>-0.00360400602221489</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003611652180552483</v>
+        <v>-0.003611680120229721</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003569101914763451</v>
+        <v>-0.003569100052118301</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003309013321995735</v>
+        <v>-0.003309018909931183</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003087164834141731</v>
+        <v>-0.00308716669678688</v>
       </c>
       <c r="JB122" t="n">
         <v>0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.00294681079685688</v>
+        <v>-0.00294683501124382</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.00267673097550869</v>
+        <v>-0.002676758915185928</v>
       </c>
       <c r="JB124" t="n">
         <v>0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.00226103700697422</v>
+        <v>-0.00226106122136116</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002160606905817986</v>
+        <v>-0.002160623669624329</v>
       </c>
       <c r="JB126" t="n">
         <v>0.9999999999999996</v>
